--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486460_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486460_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7849</v>
+        <v>8.9237</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7142</v>
+        <v>9.161199999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0707</v>
+        <v>-0.2375</v>
       </c>
       <c r="G2" t="n">
         <v>9.543900000000001</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1717</v>
+        <v>-1.0329</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6165</v>
+        <v>-0.1694</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5552</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.1952</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7898</v>
+        <v>4.5837</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1293</v>
+        <v>5.7998</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3394</v>
+        <v>-1.2161</v>
       </c>
       <c r="G3" t="n">
         <v>4.6512</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6014</v>
+        <v>-0.8075</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0274</v>
+        <v>-0.3569</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5739</v>
+        <v>-0.4506</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5649999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8355</v>
+        <v>2.9665</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9649</v>
+        <v>2.1884</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8706</v>
+        <v>0.7781</v>
       </c>
       <c r="G4" t="n">
         <v>2.8322</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5193</v>
+        <v>-1.3883</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6165</v>
+        <v>-0.3929</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9028</v>
+        <v>-0.9953</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9867</v>
+        <v>1.5069</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6686</v>
+        <v>3.0039</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.682</v>
+        <v>-1.497</v>
       </c>
       <c r="G5" t="n">
         <v>0.1119</v>
@@ -844,13 +844,13 @@
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5603</v>
+        <v>-1.0401</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.411</v>
+        <v>-0.0757</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1493</v>
+        <v>-0.9644</v>
       </c>
       <c r="V5" t="n">
         <v>1.13</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5658</v>
+        <v>0.982</v>
       </c>
       <c r="E6" t="n">
-        <v>0.232</v>
+        <v>0.6791</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3338</v>
+        <v>0.303</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2596</v>
@@ -922,13 +922,13 @@
         <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9146</v>
+        <v>-0.4984</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3509</v>
+        <v>0.0961</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5637</v>
+        <v>-0.5946</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0129</v>
+        <v>0.0179</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0129</v>
+        <v>0.0179</v>
       </c>
       <c r="G7" t="n">
         <v>0.1155</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4258</v>
+        <v>-2.5097</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8735</v>
+        <v>-1.7742</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2994</v>
+        <v>-0.7355</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.711</v>
+        <v>-0.493</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4665</v>
+        <v>-0.8699</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7555</v>
+        <v>0.3769</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.365</v>
+        <v>-0.0179</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.0313</v>
+        <v>-0.2857</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6663</v>
+        <v>0.2677</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3461</v>
+        <v>-0.4751</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4353</v>
+        <v>-0.5843</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0892</v>
+        <v>0.1091</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6525</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3926</v>
+        <v>-3.4801</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>3.0024</v>
+        <v>-0.5588</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3059</v>
+        <v>0.0288</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3034</v>
+        <v>-0.5876</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.0647</v>
+        <v>0.9347</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3252</v>
+        <v>1.695</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.3899</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. GARCIA CALVO</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.125</v>
+        <v>-3.0386</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2428</v>
+        <v>-0.5851</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1178</v>
+        <v>-2.4535</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8504</v>
+        <v>-0.711</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2289</v>
+        <v>-2.4665</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3785</v>
+        <v>1.7555</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4733</v>
+        <v>-0.365</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1251</v>
+        <v>-2.0313</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6519</v>
+        <v>1.6663</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3771</v>
+        <v>-0.3461</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1038</v>
+        <v>-0.4353</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2733</v>
+        <v>0.0892</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.0451</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.5676</v>
+        <v>-2.3926</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2055</v>
+        <v>0.3897</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6682</v>
+        <v>0.8472</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4627</v>
+        <v>-0.4576</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5649999999999999</v>
+        <v>-2.0647</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-3.3899</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>S. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5386</v>
+        <v>-3.572</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5565</v>
+        <v>-3.6898</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.982</v>
+        <v>0.1178</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.493</v>
+        <v>-0.8504</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8699</v>
+        <v>-1.2289</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3769</v>
+        <v>0.3785</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0179</v>
+        <v>-0.4733</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2857</v>
+        <v>-1.1251</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2677</v>
+        <v>0.6519</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4751</v>
+        <v>-0.3771</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5843</v>
+        <v>-0.1038</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1091</v>
+        <v>-0.2733</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3926</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4801</v>
+        <v>-4.5676</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5877</v>
+        <v>-0.2415</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.2211</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.4627</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9347</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7602</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.860399999999997</v>
+        <v>9.860400000000002</v>
       </c>
       <c r="E11" t="n">
-        <v>14.7832</v>
+        <v>14.7833</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.9228</v>
+        <v>-4.922800000000001</v>
       </c>
       <c r="G11" t="n">
         <v>14.9407</v>
@@ -1288,7 +1288,7 @@
         <v>17.1176</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3514000000000007</v>
+        <v>0.3514000000000002</v>
       </c>
       <c r="L11" t="n">
         <v>16.7662</v>
@@ -1312,16 +1312,16 @@
         <v>11.9627</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.275600000000001</v>
+        <v>-5.275399999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1982999999999996</v>
+        <v>0.1982999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.4737</v>
+        <v>-5.4738</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1951999999999997</v>
+        <v>0.1951999999999996</v>
       </c>
       <c r="W11" t="n">
         <v>9.430299999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.4853</v>
+        <v>4.3562</v>
       </c>
       <c r="E12" t="n">
-        <v>5.3951</v>
+        <v>6.5127</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9098</v>
+        <v>-2.1564</v>
       </c>
       <c r="G12" t="n">
         <v>4.4225</v>
@@ -1390,13 +1390,13 @@
         <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2195</v>
+        <v>-0.3485</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2329</v>
+        <v>-0.1153</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0134</v>
+        <v>-0.2331</v>
       </c>
       <c r="V12" t="n">
         <v>0.9347</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2229</v>
+        <v>2.402</v>
       </c>
       <c r="E13" t="n">
-        <v>2.867</v>
+        <v>1.8612</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3559</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>1.2994</v>
@@ -1468,13 +1468,13 @@
         <v>0.435</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4884</v>
+        <v>0.6675</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9612</v>
+        <v>0.9554</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4728</v>
+        <v>-0.2878</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>J. LOBO MARTORELL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8818</v>
+        <v>0.5875</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1385</v>
+        <v>1.4693</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2567</v>
+        <v>-0.8818</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-2.1689</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1641</v>
+        <v>-0.733</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6742</v>
+        <v>-1.4359</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2441</v>
+        <v>-0.6141</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5173</v>
+        <v>-0.5991</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7267</v>
+        <v>-0.0151</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.0823</v>
+        <v>-1.5548</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6814</v>
+        <v>-0.1339</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4009</v>
+        <v>-1.4208</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R14" t="n">
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0023</v>
+        <v>0.149</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9167</v>
+        <v>0.3461</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0856</v>
+        <v>-0.1971</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9347</v>
+        <v>2.8249</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1952</v>
+        <v>2.8249</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. LOBO MARTORELL</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4298</v>
+        <v>0.1611</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5753</v>
+        <v>2.3562</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0051</v>
+        <v>-2.195</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1689</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.733</v>
+        <v>-0.1641</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4359</v>
+        <v>-0.6742</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6141</v>
+        <v>1.2441</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5991</v>
+        <v>0.5173</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0151</v>
+        <v>0.7267</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5548</v>
+        <v>-2.0823</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1339</v>
+        <v>-0.6814</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4208</v>
+        <v>-1.4009</v>
       </c>
       <c r="P15" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-0.2175</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8683</v>
+        <v>1.2816</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.548</v>
+        <v>1.1344</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3204</v>
+        <v>0.1472</v>
       </c>
       <c r="V15" t="n">
-        <v>2.8249</v>
+        <v>-0.9347</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8249</v>
+        <v>0.1952</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.637</v>
+        <v>-0.3518</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2796</v>
+        <v>-0.0561</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3574</v>
+        <v>-0.2957</v>
       </c>
       <c r="G16" t="n">
         <v>-2.1061</v>
@@ -1702,13 +1702,13 @@
         <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1216</v>
+        <v>0.4068</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0805</v>
+        <v>0.304</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0411</v>
+        <v>0.1027</v>
       </c>
       <c r="V16" t="n">
         <v>1.13</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7572</v>
+        <v>-0.7957</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5018</v>
+        <v>-0.7254</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2553</v>
+        <v>-0.0704</v>
       </c>
       <c r="G17" t="n">
         <v>0.7328</v>
@@ -1780,13 +1780,13 @@
         <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6629</v>
+        <v>0.6243</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6886</v>
+        <v>0.4651</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0257</v>
+        <v>0.1592</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8393</v>
+        <v>-1.163</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2682</v>
+        <v>-0.1788</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1075</v>
+        <v>-0.9842</v>
       </c>
       <c r="G18" t="n">
         <v>-4.0451</v>
@@ -1858,13 +1858,13 @@
         <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7708</v>
+        <v>0.447</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7487</v>
+        <v>0.3016</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0221</v>
+        <v>0.1454</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5237</v>
+        <v>-1.5756</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6895</v>
+        <v>-0.1249</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-1.4507</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3641</v>
@@ -1936,13 +1936,13 @@
         <v>1.9576</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0721</v>
+        <v>0.876</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8663999999999999</v>
+        <v>0.6982</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7943</v>
+        <v>0.1778</v>
       </c>
       <c r="V19" t="n">
         <v>0.5649999999999999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6313</v>
+        <v>-3.5023</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7671</v>
+        <v>-1.8846</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8643</v>
+        <v>-1.6177</v>
       </c>
       <c r="G20" t="n">
         <v>-4.228</v>
@@ -2014,13 +2014,13 @@
         <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>1.7266</v>
+        <v>0.8556</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1138</v>
+        <v>0.9962</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3872</v>
+        <v>-0.1406</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5649999999999999</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5552</v>
+        <v>-4.8904</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7578</v>
+        <v>-2.0931</v>
       </c>
       <c r="F21" t="n">
         <v>-2.7973</v>
@@ -2092,10 +2092,10 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9866</v>
+        <v>0.6513</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0911</v>
+        <v>0.7559</v>
       </c>
       <c r="U21" t="n">
         <v>-0.1046</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0768</v>
+        <v>-5.0884</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3253</v>
+        <v>-2.2136</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7515</v>
+        <v>-2.8748</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2756</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3237</v>
+        <v>-0.3353</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1557</v>
+        <v>0.0324</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2599</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.860300000000001</v>
+        <v>-9.860399999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>4.923</v>
+        <v>4.922899999999998</v>
       </c>
       <c r="F23" t="n">
         <v>-14.7832</v>
@@ -2248,13 +2248,13 @@
         <v>11.9629</v>
       </c>
       <c r="S23" t="n">
-        <v>5.275600000000001</v>
+        <v>5.2753</v>
       </c>
       <c r="T23" t="n">
-        <v>5.4738</v>
+        <v>5.4739</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1985</v>
+        <v>-0.1984999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1951000000000005</v>
